--- a/statistics/HasteBoots_Performance.xlsx
+++ b/statistics/HasteBoots_Performance.xlsx
@@ -5,19 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/freya/Library/Mobile Documents/com~apple~CloudDocs/ProjectsSync/zkfhe/performance/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/freya/Code/zkp/HasteBoots/statistics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F99818-3CB4-5844-8BD1-A885F6BA20D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD928BE-899D-DB4B-B01A-597CF417FC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38800" yWindow="-5740" windowWidth="33720" windowHeight="21100" activeTab="4" xr2:uid="{C673FD5D-B71E-674D-A3F8-C614E287E2BF}"/>
+    <workbookView xWindow="34920" yWindow="-5740" windowWidth="33720" windowHeight="21100" activeTab="1" xr2:uid="{C673FD5D-B71E-674D-A3F8-C614E287E2BF}"/>
   </bookViews>
   <sheets>
-    <sheet name="FHE Param Sets" sheetId="2" r:id="rId1"/>
-    <sheet name="Other Machines" sheetId="5" r:id="rId2"/>
-    <sheet name="FHE Parameters" sheetId="1" r:id="rId3"/>
-    <sheet name="PCS Perforamance" sheetId="3" r:id="rId4"/>
-    <sheet name="Batch Perforamance" sheetId="4" r:id="rId5"/>
+    <sheet name="Table 2" sheetId="2" r:id="rId1"/>
+    <sheet name="Table 4" sheetId="4" r:id="rId2"/>
+    <sheet name="PCS Perforamance" sheetId="3" r:id="rId3"/>
+    <sheet name="FHE Parameters" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="123">
   <si>
     <t>Parameter Set</t>
   </si>
@@ -440,12 +439,6 @@
     <t>1 PBS</t>
   </si>
   <si>
-    <t>Batched Blind Rotation with Brakedown</t>
-  </si>
-  <si>
-    <t>Batched Blind Rotation with Dory</t>
-  </si>
-  <si>
     <t>poly</t>
   </si>
   <si>
@@ -482,13 +475,7 @@
     <t>Batched PBS with Brakedown</t>
   </si>
   <si>
-    <t>M4 Pro Max</t>
-  </si>
-  <si>
     <t>Batched PBS with Dory</t>
-  </si>
-  <si>
-    <t>C6i.metal</t>
   </si>
 </sst>
 </file>
@@ -783,7 +770,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -837,41 +824,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1249,8 +1230,8 @@
       <c r="G3" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="54" t="s">
-        <v>118</v>
+      <c r="H3" s="52" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -1272,8 +1253,8 @@
       <c r="G4" s="38">
         <v>13</v>
       </c>
-      <c r="H4" s="55" t="s">
-        <v>121</v>
+      <c r="H4" s="53" t="s">
+        <v>119</v>
       </c>
       <c r="I4" t="s">
         <v>10</v>
@@ -1298,8 +1279,8 @@
       <c r="G5" s="38">
         <v>4</v>
       </c>
-      <c r="H5" s="54" t="s">
-        <v>119</v>
+      <c r="H5" s="52" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -1321,8 +1302,8 @@
       <c r="G6" s="38">
         <v>8</v>
       </c>
-      <c r="H6" s="54" t="s">
-        <v>120</v>
+      <c r="H6" s="52" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -1389,7 +1370,7 @@
       <c r="L10" s="43"/>
       <c r="M10" s="43"/>
       <c r="N10" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -1789,17 +1770,17 @@
       </c>
     </row>
     <row r="23" spans="1:14" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="56" t="s">
+      <c r="B23" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="57"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B24" s="38" t="s">
@@ -1974,7 +1955,7 @@
       <c r="B36" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="51">
+      <c r="C36" s="49">
         <v>7.97</v>
       </c>
       <c r="D36" s="21">
@@ -4332,848 +4313,1596 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F40CA5BF-1F27-F540-B503-59C389FBCD9E}">
-  <dimension ref="A6:N38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10F5213-1942-4945-915F-4EC6808BC28C}">
+  <dimension ref="A4:X55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="6.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="7" customWidth="1"/>
+    <col min="7" max="7" width="8.5" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="8.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B6" s="56" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B7" s="38" t="s">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B4" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C4" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="38" t="s">
+        <v>5</v>
+      </c>
+      <c r="P4" s="15"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B5" s="38"/>
+      <c r="C5" s="38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="38">
+        <v>728</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="38">
+        <v>4</v>
+      </c>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="54"/>
+      <c r="U7" s="54"/>
+      <c r="V7" s="54"/>
+      <c r="W7" s="54"/>
+      <c r="X7" s="54"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C8" s="69" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="54"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="54"/>
+      <c r="U8" s="54"/>
+      <c r="V8" s="54"/>
+      <c r="W8" s="54"/>
+      <c r="X8" s="54"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B9" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L9" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="O9" s="54"/>
+      <c r="P9" s="54"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="54"/>
+      <c r="U9" s="54"/>
+      <c r="V9" s="54"/>
+      <c r="W9" s="54"/>
+      <c r="X9" s="54"/>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B10" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="51">
+        <v>3.5100000000000002</v>
+      </c>
+      <c r="D10" s="21">
+        <v>0.61199999999999988</v>
+      </c>
+      <c r="E10" s="21">
+        <v>17.436</v>
+      </c>
+      <c r="F10" s="21">
+        <v>2.8980000000000001</v>
+      </c>
+      <c r="G10" s="21">
+        <v>224.24</v>
+      </c>
+      <c r="H10" s="21">
+        <v>222.81</v>
+      </c>
+      <c r="I10" s="21">
+        <v>99.36</v>
+      </c>
+      <c r="J10" s="21">
+        <v>1.4300000000000002</v>
+      </c>
+      <c r="K10" s="21">
+        <v>135.44881000000004</v>
+      </c>
+      <c r="L10" s="21">
+        <v>135.27241000000001</v>
+      </c>
+      <c r="M10" s="21">
+        <v>99.87</v>
+      </c>
+      <c r="N10" s="24">
+        <v>0.17641000000000004</v>
+      </c>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="54"/>
+      <c r="X10" s="54"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B11" s="46">
         <v>1</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="C11" s="10">
+        <v>3.15</v>
+      </c>
+      <c r="D11">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E11">
+        <v>17.59</v>
+      </c>
+      <c r="F11">
+        <v>2.6</v>
+      </c>
+      <c r="G11">
+        <v>200.42</v>
+      </c>
+      <c r="H11">
+        <v>199.17</v>
+      </c>
+      <c r="I11">
+        <v>99.38</v>
+      </c>
+      <c r="J11">
+        <v>1.25</v>
+      </c>
+      <c r="K11">
+        <v>135.4511</v>
+      </c>
+      <c r="L11">
+        <v>135.27420000000001</v>
+      </c>
+      <c r="M11">
+        <v>99.87</v>
+      </c>
+      <c r="N11" s="50">
+        <v>0.1769</v>
+      </c>
+      <c r="O11" s="54"/>
+      <c r="P11" s="55"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="55"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="54"/>
+      <c r="X11" s="54"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B12" s="46">
         <v>2</v>
       </c>
-      <c r="E7" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="38" t="s">
+      <c r="C12" s="10">
+        <v>5.35</v>
+      </c>
+      <c r="D12">
+        <v>0.84</v>
+      </c>
+      <c r="E12">
+        <v>15.78</v>
+      </c>
+      <c r="F12">
+        <v>4.51</v>
+      </c>
+      <c r="G12">
+        <v>287.37</v>
+      </c>
+      <c r="H12">
+        <v>286.06</v>
+      </c>
+      <c r="I12">
+        <v>99.54</v>
+      </c>
+      <c r="J12">
+        <v>1.31</v>
+      </c>
+      <c r="K12">
+        <v>169.92619999999999</v>
+      </c>
+      <c r="L12">
+        <v>169.7474</v>
+      </c>
+      <c r="M12">
+        <v>99.89</v>
+      </c>
+      <c r="N12" s="50">
+        <v>0.17879999999999999</v>
+      </c>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="55"/>
+      <c r="S12" s="55"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="54"/>
+      <c r="V12" s="54"/>
+      <c r="W12" s="54"/>
+      <c r="X12" s="54"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B13" s="46">
         <v>4</v>
       </c>
-      <c r="G7" s="38" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="38">
-        <v>728</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="38" t="s">
+      <c r="C13" s="10">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D13">
+        <v>1.58</v>
+      </c>
+      <c r="E13">
+        <v>15.48</v>
+      </c>
+      <c r="F13">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="G13">
+        <v>365.68</v>
+      </c>
+      <c r="H13">
+        <v>363.71</v>
+      </c>
+      <c r="I13">
+        <v>99.46</v>
+      </c>
+      <c r="J13">
+        <v>1.97</v>
+      </c>
+      <c r="K13">
+        <v>196.85040000000001</v>
+      </c>
+      <c r="L13">
+        <v>196.6678</v>
+      </c>
+      <c r="M13">
+        <v>99.91</v>
+      </c>
+      <c r="N13" s="50">
+        <v>0.18260000000000001</v>
+      </c>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="54"/>
+      <c r="U13" s="54"/>
+      <c r="V13" s="54"/>
+      <c r="W13" s="54"/>
+      <c r="X13" s="54"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B14" s="46">
         <v>8</v>
       </c>
-      <c r="G8" s="38">
-        <v>13</v>
-      </c>
-      <c r="H8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C14" s="10">
+        <v>20.75</v>
+      </c>
+      <c r="D14">
+        <v>3.42</v>
+      </c>
+      <c r="E14">
+        <v>16.489999999999998</v>
+      </c>
+      <c r="F14">
+        <v>17.329999999999998</v>
+      </c>
+      <c r="G14">
+        <v>521.07000000000005</v>
+      </c>
+      <c r="H14">
+        <v>519.44000000000005</v>
+      </c>
+      <c r="I14">
+        <v>99.69</v>
+      </c>
+      <c r="J14">
+        <v>1.63</v>
+      </c>
+      <c r="K14">
+        <v>250.2662</v>
+      </c>
+      <c r="L14">
+        <v>250.07669999999999</v>
+      </c>
+      <c r="M14">
+        <v>99.92</v>
+      </c>
+      <c r="N14" s="50">
+        <v>0.1895</v>
+      </c>
+      <c r="O14" s="54"/>
+      <c r="P14" s="54"/>
+      <c r="Q14" s="54"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="54"/>
+      <c r="U14" s="54"/>
+      <c r="V14" s="54"/>
+      <c r="W14" s="54"/>
+      <c r="X14" s="54"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B15" s="47">
+        <v>16</v>
+      </c>
+      <c r="C15" s="7">
+        <v>49.41</v>
+      </c>
+      <c r="D15" s="3">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="E15" s="3">
+        <v>16.29</v>
+      </c>
+      <c r="F15" s="3">
+        <v>41.37</v>
+      </c>
+      <c r="G15" s="3">
+        <v>749.82</v>
+      </c>
+      <c r="H15" s="3">
+        <v>747.48</v>
+      </c>
+      <c r="I15" s="3">
+        <v>99.69</v>
+      </c>
+      <c r="J15" s="3">
+        <v>2.34</v>
+      </c>
+      <c r="K15" s="3">
+        <v>293.2978</v>
+      </c>
+      <c r="L15" s="3">
+        <v>293.09309999999999</v>
+      </c>
+      <c r="M15" s="3">
+        <v>99.93</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0.20469999999999999</v>
+      </c>
+      <c r="O15" s="54"/>
+      <c r="P15" s="54"/>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="31"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="54"/>
+      <c r="U15" s="54"/>
+      <c r="V15" s="54"/>
+      <c r="W15" s="54"/>
+      <c r="X15" s="54"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="O16" s="54"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="54"/>
+      <c r="U16" s="54"/>
+      <c r="V16" s="54"/>
+      <c r="W16" s="54"/>
+      <c r="X16" s="54"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="O17" s="54"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="54"/>
+      <c r="S17" s="54"/>
+      <c r="T17" s="54"/>
+      <c r="U17" s="54"/>
+      <c r="V17" s="54"/>
+      <c r="W17" s="54"/>
+      <c r="X17" s="54"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="O18" s="54"/>
+      <c r="P18" s="54"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="54"/>
+      <c r="S18" s="54"/>
+      <c r="T18" s="54"/>
+      <c r="U18" s="54"/>
+      <c r="V18" s="54"/>
+      <c r="W18" s="54"/>
+      <c r="X18" s="54"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A19" s="54"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="54"/>
+      <c r="K19" s="54"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="54"/>
+      <c r="N19" s="54"/>
+      <c r="O19" s="54"/>
+      <c r="P19" s="54"/>
+      <c r="Q19" s="54"/>
+      <c r="R19" s="54"/>
+      <c r="S19" s="54"/>
+      <c r="T19" s="54"/>
+      <c r="U19" s="54"/>
+      <c r="V19" s="54"/>
+      <c r="W19" s="54"/>
+      <c r="X19" s="54"/>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A20" s="54"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="54"/>
+      <c r="K20" s="54"/>
+      <c r="L20" s="54"/>
+      <c r="M20" s="54"/>
+      <c r="N20" s="54"/>
+      <c r="O20" s="54"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="54"/>
+      <c r="R20" s="54"/>
+      <c r="S20" s="54"/>
+      <c r="T20" s="54"/>
+      <c r="U20" s="54"/>
+      <c r="V20" s="54"/>
+      <c r="W20" s="54"/>
+      <c r="X20" s="54"/>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="O21" s="54"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="54"/>
+      <c r="R21" s="54"/>
+      <c r="S21" s="54"/>
+      <c r="T21" s="54"/>
+      <c r="U21" s="54"/>
+      <c r="V21" s="54"/>
+      <c r="W21" s="54"/>
+      <c r="X21" s="54"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C22" s="69" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="L22" s="69"/>
+      <c r="M22" s="69"/>
+      <c r="N22" s="69"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q22" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="R22" s="33"/>
+      <c r="S22" s="33"/>
+      <c r="T22" s="33"/>
+      <c r="U22" s="33"/>
+      <c r="V22" s="33"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="54"/>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L23" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="O23" s="54"/>
+      <c r="P23" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q23" s="56">
+        <v>22</v>
+      </c>
+      <c r="R23" s="56">
+        <v>23</v>
+      </c>
+      <c r="S23" s="56">
+        <v>24</v>
+      </c>
+      <c r="T23" s="56">
+        <v>25</v>
+      </c>
+      <c r="U23" s="56">
+        <v>26</v>
+      </c>
+      <c r="V23" s="56">
+        <v>27</v>
+      </c>
+      <c r="W23" s="57">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="18">
-        <v>25</v>
-      </c>
-      <c r="D11" s="19">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="14">
+      <c r="X23" s="54"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B24" s="46" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="51">
+        <v>5.4716640000000005</v>
+      </c>
+      <c r="D24" s="21">
+        <v>2.573664</v>
+      </c>
+      <c r="E24" s="21">
+        <v>47.036221522374177</v>
+      </c>
+      <c r="F24" s="21">
+        <v>2.8980000000000001</v>
+      </c>
+      <c r="G24" s="21">
+        <f>J24+H24</f>
+        <v>109.35000000000001</v>
+      </c>
+      <c r="H24" s="21">
+        <v>107.92</v>
+      </c>
+      <c r="I24" s="21">
+        <v>98.692272519433004</v>
+      </c>
+      <c r="J24" s="21">
+        <v>1.4300000000000002</v>
+      </c>
+      <c r="K24" s="21">
+        <f>L24+N24</f>
+        <v>0.23746800000000004</v>
+      </c>
+      <c r="L24" s="21">
+        <v>6.1058000000000001E-2</v>
+      </c>
+      <c r="M24" s="21">
+        <v>25.712095945558978</v>
+      </c>
+      <c r="N24" s="24">
+        <v>0.17641000000000004</v>
+      </c>
+      <c r="O24" s="54"/>
+      <c r="P24" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q24" s="58">
+        <v>0.30944899999999997</v>
+      </c>
+      <c r="R24" s="58">
+        <v>0.580986</v>
+      </c>
+      <c r="S24" s="58">
+        <v>1.1536900000000001</v>
+      </c>
+      <c r="T24" s="58">
+        <v>1.981185</v>
+      </c>
+      <c r="U24" s="58">
+        <v>4.0958680000000003</v>
+      </c>
+      <c r="V24" s="33">
+        <v>6.77</v>
+      </c>
+      <c r="W24" s="59">
+        <v>13.69</v>
+      </c>
+      <c r="X24" s="54"/>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="46">
+        <v>1</v>
+      </c>
+      <c r="C25" s="51">
+        <f>D25+F25</f>
+        <v>5.1736640000000005</v>
+      </c>
+      <c r="D25" s="21">
+        <v>2.573664</v>
+      </c>
+      <c r="F25">
+        <v>2.6</v>
+      </c>
+      <c r="G25" s="21">
+        <f t="shared" ref="G25:G29" si="0">J25+H25</f>
+        <v>109.17</v>
+      </c>
+      <c r="H25" s="21">
+        <v>107.92</v>
+      </c>
+      <c r="J25">
+        <v>1.25</v>
+      </c>
+      <c r="K25" s="21">
+        <f t="shared" ref="K25:K29" si="1">L25+N25</f>
+        <v>0.237958</v>
+      </c>
+      <c r="L25" s="21">
+        <v>6.1058000000000001E-2</v>
+      </c>
+      <c r="M25" s="21"/>
+      <c r="N25" s="50">
+        <v>0.1769</v>
+      </c>
+      <c r="O25" s="54"/>
+      <c r="P25" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q25" s="58">
+        <v>0.40713100000000002</v>
+      </c>
+      <c r="R25" s="58">
+        <v>0.665489</v>
+      </c>
+      <c r="S25" s="58">
+        <v>0.70998700000000003</v>
+      </c>
+      <c r="T25" s="58">
+        <v>1.2236100000000001</v>
+      </c>
+      <c r="U25" s="58">
+        <v>1.3767259999999999</v>
+      </c>
+      <c r="V25" s="33">
+        <v>2.48</v>
+      </c>
+      <c r="W25" s="59">
+        <v>2.92</v>
+      </c>
+      <c r="X25" s="54"/>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="46">
         <v>2</v>
       </c>
-      <c r="D12" s="20">
-        <v>1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B13" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="31">
-        <v>27.251169999999998</v>
-      </c>
-      <c r="D13" s="24">
-        <v>13.625584999999999</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B14" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="21">
-        <v>89.091453999999999</v>
-      </c>
-      <c r="D14" s="24">
-        <v>44.545726999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B15" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="21">
-        <v>3.2454999999999998</v>
-      </c>
-      <c r="D15" s="24">
-        <v>1.6227499999999999</v>
-      </c>
-      <c r="F15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B16" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="25">
-        <v>3.085906</v>
-      </c>
-      <c r="D16" s="26">
-        <v>1.542953</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="18">
-        <v>26</v>
-      </c>
-      <c r="D17" s="19">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B19" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="51">
-        <v>7.97</v>
-      </c>
-      <c r="D19" s="21">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="24">
-        <v>1.43</v>
-      </c>
-      <c r="D20" s="21">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B21" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="24">
-        <v>58.35</v>
-      </c>
-      <c r="D21" s="21">
-        <v>58.35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B22" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="26">
+      <c r="C26" s="51">
+        <f t="shared" ref="C26:C29" si="2">D26+F26</f>
+        <v>8.9384049999999995</v>
+      </c>
+      <c r="D26">
+        <v>4.4284049999999997</v>
+      </c>
+      <c r="F26">
+        <v>4.51</v>
+      </c>
+      <c r="G26" s="21">
+        <f t="shared" si="0"/>
+        <v>118.17</v>
+      </c>
+      <c r="H26">
+        <v>116.86</v>
+      </c>
+      <c r="J26">
+        <v>1.31</v>
+      </c>
+      <c r="K26" s="21">
+        <f t="shared" si="1"/>
+        <v>0.24480199999999999</v>
+      </c>
+      <c r="L26" s="21">
+        <v>6.6002000000000005E-2</v>
+      </c>
+      <c r="M26" s="21"/>
+      <c r="N26" s="50">
+        <v>0.17879999999999999</v>
+      </c>
+      <c r="O26" s="54"/>
+      <c r="P26" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q26" s="58">
+        <v>49.74</v>
+      </c>
+      <c r="R26" s="58">
+        <v>54.15</v>
+      </c>
+      <c r="S26" s="58">
+        <v>53.96</v>
+      </c>
+      <c r="T26" s="58">
+        <v>58.43</v>
+      </c>
+      <c r="U26" s="58">
+        <v>57.96</v>
+      </c>
+      <c r="V26" s="33">
+        <v>62.11</v>
+      </c>
+      <c r="W26" s="59">
+        <v>61.83</v>
+      </c>
+      <c r="X26" s="54"/>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="46">
+        <v>4</v>
+      </c>
+      <c r="C27" s="51">
+        <f t="shared" si="2"/>
+        <v>15.46932</v>
+      </c>
+      <c r="D27">
+        <v>6.8493200000000005</v>
+      </c>
+      <c r="F27">
+        <v>8.6199999999999992</v>
+      </c>
+      <c r="G27" s="21">
+        <f t="shared" si="0"/>
+        <v>117.89</v>
+      </c>
+      <c r="H27">
+        <v>115.92</v>
+      </c>
+      <c r="J27">
+        <v>1.97</v>
+      </c>
+      <c r="K27" s="21">
+        <f t="shared" si="1"/>
+        <v>0.24860200000000002</v>
+      </c>
+      <c r="L27" s="21">
+        <v>6.6002000000000005E-2</v>
+      </c>
+      <c r="M27" s="21"/>
+      <c r="N27" s="50">
+        <v>0.18260000000000001</v>
+      </c>
+      <c r="O27" s="54"/>
+      <c r="P27" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q27" s="60">
+        <v>2.8056999999999999E-2</v>
+      </c>
+      <c r="R27" s="60">
+        <v>3.0529000000000001E-2</v>
+      </c>
+      <c r="S27" s="60">
+        <v>3.0529000000000001E-2</v>
+      </c>
+      <c r="T27" s="60">
         <v>3.3001000000000003E-2</v>
       </c>
-      <c r="D22" s="25">
+      <c r="U27" s="60">
         <v>3.3001000000000003E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B23" s="9"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B24" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" s="5" t="s">
+      <c r="V27" s="61">
+        <v>0.04</v>
+      </c>
+      <c r="W27" s="62">
+        <v>0.04</v>
+      </c>
+      <c r="X27" s="54"/>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="46">
+        <v>8</v>
+      </c>
+      <c r="C28" s="51">
+        <f t="shared" si="2"/>
+        <v>29.06</v>
+      </c>
+      <c r="D28">
+        <v>11.73</v>
+      </c>
+      <c r="F28">
+        <v>17.329999999999998</v>
+      </c>
+      <c r="G28" s="21">
+        <f t="shared" si="0"/>
+        <v>125.85</v>
+      </c>
+      <c r="H28">
+        <v>124.22</v>
+      </c>
+      <c r="J28">
+        <v>1.63</v>
+      </c>
+      <c r="K28" s="21">
+        <f t="shared" si="1"/>
+        <v>0.26950000000000002</v>
+      </c>
+      <c r="L28" s="21">
+        <v>0.08</v>
+      </c>
+      <c r="N28" s="50">
+        <v>0.1895</v>
+      </c>
+      <c r="O28" s="54"/>
+      <c r="P28" s="54"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="54"/>
+      <c r="W28" s="54"/>
+      <c r="X28" s="54"/>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="47">
         <v>16</v>
       </c>
-      <c r="K24" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="L24" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="N24" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B25" s="10">
-        <v>1</v>
-      </c>
-      <c r="C25">
-        <v>14.3</v>
-      </c>
-      <c r="D25">
-        <v>4.46</v>
-      </c>
-      <c r="E25">
-        <v>31.18</v>
-      </c>
-      <c r="F25">
-        <v>9.84</v>
-      </c>
-      <c r="G25">
-        <v>884.53</v>
-      </c>
-      <c r="H25">
-        <v>881.64</v>
-      </c>
-      <c r="I25">
-        <v>99.67</v>
-      </c>
-      <c r="J25">
-        <v>2.89</v>
-      </c>
-      <c r="K25">
-        <v>181.477</v>
-      </c>
-      <c r="L25">
-        <v>181.3272</v>
-      </c>
-      <c r="M25">
-        <v>99.92</v>
-      </c>
-      <c r="N25">
-        <v>0.14979999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B26" s="10">
-        <v>2</v>
-      </c>
-      <c r="C26">
-        <v>13.15</v>
-      </c>
-      <c r="D26">
-        <v>3.57</v>
-      </c>
-      <c r="E26">
-        <v>27.18</v>
-      </c>
-      <c r="F26">
-        <v>9.58</v>
-      </c>
-      <c r="G26">
-        <v>942.95</v>
-      </c>
-      <c r="H26">
-        <v>940.17</v>
-      </c>
-      <c r="I26">
-        <v>99.71</v>
-      </c>
-      <c r="J26">
-        <v>2.78</v>
-      </c>
-      <c r="K26">
-        <v>181.5583</v>
-      </c>
-      <c r="L26">
-        <v>181.4085</v>
-      </c>
-      <c r="M26">
-        <v>99.92</v>
-      </c>
-      <c r="N26">
-        <v>0.1497</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B27" s="10">
-        <v>3</v>
-      </c>
-      <c r="C27">
-        <v>13.33</v>
-      </c>
-      <c r="D27">
-        <v>3.69</v>
-      </c>
-      <c r="E27">
-        <v>27.65</v>
-      </c>
-      <c r="F27">
-        <v>9.65</v>
-      </c>
-      <c r="G27">
-        <v>889.68</v>
-      </c>
-      <c r="H27">
-        <v>886.91</v>
-      </c>
-      <c r="I27">
-        <v>99.69</v>
-      </c>
-      <c r="J27">
-        <v>2.77</v>
-      </c>
-      <c r="K27">
-        <v>181.63460000000001</v>
-      </c>
-      <c r="L27">
-        <v>181.48500000000001</v>
-      </c>
-      <c r="M27">
-        <v>99.92</v>
-      </c>
-      <c r="N27">
-        <v>0.14960000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B28" s="10">
-        <v>4</v>
-      </c>
-      <c r="C28">
-        <v>14.1</v>
-      </c>
-      <c r="D28">
-        <v>4.24</v>
-      </c>
-      <c r="E28">
-        <v>30.05</v>
-      </c>
-      <c r="F28">
-        <v>9.86</v>
-      </c>
-      <c r="G28">
-        <v>996.26</v>
-      </c>
-      <c r="H28">
-        <v>993.44</v>
-      </c>
-      <c r="I28">
-        <v>99.72</v>
-      </c>
-      <c r="J28">
-        <v>2.82</v>
-      </c>
-      <c r="K28">
-        <v>181.5395</v>
-      </c>
-      <c r="L28">
-        <v>181.38980000000001</v>
-      </c>
-      <c r="M28">
-        <v>99.92</v>
-      </c>
-      <c r="N28">
-        <v>0.1497</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B29" s="10">
-        <v>5</v>
-      </c>
-      <c r="C29">
-        <v>13.1</v>
-      </c>
-      <c r="D29">
-        <v>3.65</v>
-      </c>
-      <c r="E29">
-        <v>27.88</v>
-      </c>
-      <c r="F29">
-        <v>9.44</v>
-      </c>
-      <c r="G29">
-        <v>930.63</v>
-      </c>
-      <c r="H29">
-        <v>927.59</v>
-      </c>
-      <c r="I29">
-        <v>99.67</v>
-      </c>
-      <c r="J29">
-        <v>3.04</v>
-      </c>
-      <c r="K29">
-        <v>181.6294</v>
-      </c>
-      <c r="L29">
-        <v>181.47970000000001</v>
-      </c>
-      <c r="M29">
-        <v>99.92</v>
-      </c>
-      <c r="N29">
-        <v>0.14960000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B30" s="10">
-        <v>6</v>
-      </c>
-      <c r="C30">
-        <v>13.82</v>
-      </c>
-      <c r="D30">
-        <v>3.72</v>
-      </c>
-      <c r="E30">
-        <v>26.9</v>
-      </c>
-      <c r="F30">
-        <v>10.1</v>
-      </c>
-      <c r="G30">
-        <v>900.03</v>
-      </c>
-      <c r="H30">
-        <v>897.15</v>
-      </c>
-      <c r="I30">
-        <v>99.68</v>
-      </c>
-      <c r="J30">
-        <v>2.89</v>
-      </c>
-      <c r="K30">
-        <v>181.56659999999999</v>
-      </c>
-      <c r="L30">
-        <v>181.4169</v>
-      </c>
-      <c r="M30">
-        <v>99.92</v>
-      </c>
-      <c r="N30">
-        <v>0.1497</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B31" s="10">
-        <v>7</v>
-      </c>
-      <c r="C31">
-        <v>14.78</v>
-      </c>
-      <c r="D31">
-        <v>4.38</v>
-      </c>
-      <c r="E31">
-        <v>29.62</v>
-      </c>
-      <c r="F31">
-        <v>10.4</v>
-      </c>
-      <c r="G31">
-        <v>899.63</v>
-      </c>
-      <c r="H31">
-        <v>896.72</v>
-      </c>
-      <c r="I31">
-        <v>99.68</v>
-      </c>
-      <c r="J31">
-        <v>2.91</v>
-      </c>
-      <c r="K31">
-        <v>181.52379999999999</v>
-      </c>
-      <c r="L31">
-        <v>181.37379999999999</v>
-      </c>
-      <c r="M31">
-        <v>99.92</v>
-      </c>
-      <c r="N31">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B32" s="10">
-        <v>8</v>
-      </c>
-      <c r="C32">
-        <v>15.15</v>
-      </c>
-      <c r="D32">
-        <v>4.5</v>
-      </c>
-      <c r="E32">
-        <v>29.68</v>
-      </c>
-      <c r="F32">
-        <v>10.65</v>
-      </c>
-      <c r="G32">
-        <v>935.88</v>
-      </c>
-      <c r="H32">
-        <v>932.83</v>
-      </c>
-      <c r="I32">
-        <v>99.67</v>
-      </c>
-      <c r="J32">
-        <v>3.05</v>
-      </c>
-      <c r="K32">
-        <v>181.5496</v>
-      </c>
-      <c r="L32">
-        <v>181.3998</v>
-      </c>
-      <c r="M32">
-        <v>99.92</v>
-      </c>
-      <c r="N32">
-        <v>0.14979999999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B33" s="10">
-        <v>9</v>
-      </c>
-      <c r="C33">
-        <v>13.11</v>
-      </c>
-      <c r="D33">
-        <v>3.61</v>
-      </c>
-      <c r="E33">
-        <v>27.56</v>
-      </c>
-      <c r="F33">
-        <v>9.5</v>
-      </c>
-      <c r="G33">
-        <v>904.57</v>
-      </c>
-      <c r="H33">
-        <v>901.53</v>
-      </c>
-      <c r="I33">
-        <v>99.66</v>
-      </c>
-      <c r="J33">
-        <v>3.04</v>
-      </c>
-      <c r="K33">
-        <v>181.59469999999999</v>
-      </c>
-      <c r="L33">
-        <v>181.44470000000001</v>
-      </c>
-      <c r="M33">
-        <v>99.92</v>
-      </c>
-      <c r="N33">
-        <v>0.15</v>
-      </c>
+      <c r="C29" s="65">
+        <f t="shared" si="2"/>
+        <v>60.9</v>
+      </c>
+      <c r="D29" s="3">
+        <v>19.53</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3">
+        <v>41.37</v>
+      </c>
+      <c r="G29" s="25">
+        <f t="shared" si="0"/>
+        <v>126</v>
+      </c>
+      <c r="H29" s="3">
+        <v>123.66</v>
+      </c>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3">
+        <v>2.34</v>
+      </c>
+      <c r="K29" s="25">
+        <f t="shared" si="1"/>
+        <v>0.28470000000000001</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="M29" s="3"/>
+      <c r="N29" s="8">
+        <v>0.20469999999999999</v>
+      </c>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="54"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="54"/>
+      <c r="V29" s="54"/>
+      <c r="W29" s="54"/>
+      <c r="X29" s="54"/>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A30" s="54"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="54"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="54"/>
+      <c r="M30" s="54"/>
+      <c r="N30" s="54"/>
+      <c r="O30" s="54"/>
+      <c r="P30" s="54"/>
+      <c r="Q30" s="54"/>
+      <c r="R30" s="54"/>
+      <c r="S30" s="54"/>
+      <c r="T30" s="54"/>
+      <c r="U30" s="54"/>
+      <c r="V30" s="54"/>
+      <c r="W30" s="54"/>
+      <c r="X30" s="54"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A31" s="54"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="54"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="54"/>
+      <c r="K31" s="54"/>
+      <c r="L31" s="54"/>
+      <c r="M31" s="54"/>
+      <c r="N31" s="54"/>
+      <c r="O31" s="54"/>
+      <c r="P31" s="54"/>
+      <c r="Q31" s="54"/>
+      <c r="R31" s="54"/>
+      <c r="S31" s="54"/>
+      <c r="T31" s="54"/>
+      <c r="U31" s="54"/>
+      <c r="V31" s="54"/>
+      <c r="W31" s="54"/>
+      <c r="X31" s="54"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B34" s="10">
-        <v>10</v>
-      </c>
-      <c r="C34">
-        <v>14.62</v>
-      </c>
-      <c r="D34">
-        <v>4.18</v>
-      </c>
-      <c r="E34">
-        <v>28.56</v>
-      </c>
-      <c r="F34">
-        <v>10.44</v>
-      </c>
-      <c r="G34">
-        <v>893.62</v>
-      </c>
-      <c r="H34">
-        <v>891.03</v>
-      </c>
-      <c r="I34">
-        <v>99.71</v>
-      </c>
-      <c r="J34">
-        <v>2.59</v>
-      </c>
-      <c r="K34">
-        <v>181.6071</v>
-      </c>
-      <c r="L34">
-        <v>181.45760000000001</v>
-      </c>
-      <c r="M34">
-        <v>99.92</v>
-      </c>
-      <c r="N34">
-        <v>0.14940000000000001</v>
-      </c>
+      <c r="A34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>126</v>
-      </c>
-      <c r="B35" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="40">
-        <f t="shared" ref="C35:N35" si="0">SUM(C25:C34)/10</f>
-        <v>13.946000000000002</v>
-      </c>
-      <c r="D35" s="41">
-        <f t="shared" si="0"/>
-        <v>3.9999999999999991</v>
-      </c>
-      <c r="E35" s="40">
-        <f t="shared" si="0"/>
-        <v>28.625999999999998</v>
-      </c>
-      <c r="F35" s="41">
-        <f t="shared" si="0"/>
-        <v>9.9460000000000015</v>
-      </c>
-      <c r="G35" s="40">
-        <f t="shared" si="0"/>
-        <v>917.77800000000002</v>
-      </c>
-      <c r="H35" s="41">
-        <f t="shared" si="0"/>
-        <v>914.90100000000007</v>
-      </c>
-      <c r="I35" s="40">
-        <f t="shared" si="0"/>
-        <v>99.685999999999993</v>
-      </c>
-      <c r="J35" s="41">
-        <f t="shared" si="0"/>
-        <v>2.8780000000000001</v>
-      </c>
-      <c r="K35" s="41">
-        <f t="shared" si="0"/>
-        <v>181.56806</v>
-      </c>
-      <c r="L35" s="40">
-        <f t="shared" si="0"/>
-        <v>181.41829999999999</v>
-      </c>
-      <c r="M35" s="41">
-        <f t="shared" si="0"/>
-        <v>99.919999999999987</v>
-      </c>
-      <c r="N35" s="41">
-        <f t="shared" si="0"/>
-        <v>0.14972999999999997</v>
-      </c>
+      <c r="C35" s="68"/>
+      <c r="D35" s="68"/>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="68"/>
+      <c r="H35" s="68"/>
+      <c r="I35" s="68"/>
+      <c r="J35" s="68"/>
+      <c r="K35" s="68"/>
+      <c r="L35" s="68"/>
+      <c r="M35" s="68"/>
+      <c r="N35" s="68"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B36" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="C36" s="40">
-        <f>D36+F35</f>
-        <v>16.536000000000001</v>
-      </c>
-      <c r="D36" s="41">
-        <f>C20+D20+D19</f>
-        <v>6.59</v>
-      </c>
-      <c r="E36" s="40">
-        <f>D36/C36*100</f>
-        <v>39.85244315432994</v>
-      </c>
-      <c r="F36" s="41"/>
-      <c r="G36" s="40">
-        <f>H36+J35</f>
-        <v>119.578</v>
-      </c>
-      <c r="H36" s="41">
-        <f>C21+D21</f>
-        <v>116.7</v>
-      </c>
-      <c r="I36" s="40">
-        <f>H36/G36*100</f>
-        <v>97.593202763050058</v>
-      </c>
-      <c r="J36" s="41"/>
-      <c r="K36" s="41">
-        <f>L36+N35</f>
-        <v>0.21573199999999998</v>
-      </c>
-      <c r="L36" s="40">
-        <f>C22+D22</f>
-        <v>6.6002000000000005E-2</v>
-      </c>
-      <c r="M36" s="41">
-        <f>L36/K36*100</f>
-        <v>30.594441251182026</v>
-      </c>
-      <c r="N36" s="41"/>
+      <c r="C36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="L36" s="2"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="40">
-        <f>D37+F35</f>
-        <v>157.208766</v>
-      </c>
-      <c r="D37" s="41">
-        <f>C14+D14+D13</f>
-        <v>147.262766</v>
-      </c>
-      <c r="E37" s="40">
-        <f>D37/C37*100</f>
-        <v>93.673380783359121</v>
-      </c>
-      <c r="F37" s="41"/>
-      <c r="G37" s="40">
-        <f>H37+J35</f>
-        <v>7.7462499999999999</v>
-      </c>
-      <c r="H37" s="41">
-        <f>C15+D15</f>
-        <v>4.8682499999999997</v>
-      </c>
-      <c r="I37" s="40">
-        <f>H37/G37*100</f>
-        <v>62.846538647732771</v>
-      </c>
-      <c r="J37" s="41"/>
-      <c r="K37" s="41">
-        <f>L37+N35</f>
-        <v>4.9283190000000001</v>
-      </c>
-      <c r="L37" s="40">
-        <f>N35+D16*3</f>
-        <v>4.7785890000000002</v>
-      </c>
-      <c r="M37" s="41">
-        <f>L37/K37*100</f>
-        <v>96.96184439359547</v>
-      </c>
-      <c r="N37" s="41"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="E38" s="21"/>
-      <c r="I38" s="21"/>
-      <c r="M38" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
+      <c r="M37" s="21"/>
+      <c r="N37" s="21"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A47" s="14"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="C48" s="68"/>
+      <c r="D48" s="68"/>
+      <c r="E48" s="68"/>
+      <c r="F48" s="68"/>
+      <c r="G48" s="68"/>
+      <c r="H48" s="68"/>
+      <c r="I48" s="68"/>
+      <c r="J48" s="68"/>
+      <c r="K48" s="68"/>
+      <c r="L48" s="68"/>
+      <c r="M48" s="68"/>
+      <c r="N48" s="68"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="L49" s="2"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C50" s="21"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="21"/>
+      <c r="G50" s="21"/>
+      <c r="H50" s="27"/>
+      <c r="I50" s="27"/>
+      <c r="J50" s="21"/>
+      <c r="K50" s="21"/>
+      <c r="L50" s="27"/>
+      <c r="M50" s="27"/>
+      <c r="N50" s="21"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C51" s="21"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="63"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="27"/>
+      <c r="I51" s="63"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="27"/>
+      <c r="M51" s="64"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C52" s="21"/>
+      <c r="G52" s="21"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="21"/>
+      <c r="M52" s="21"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="21"/>
+      <c r="M53" s="21"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C55" s="21"/>
+      <c r="G55" s="21"/>
+      <c r="K55" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B6:J6"/>
+  <mergeCells count="12">
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="K35:N35"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="G48:J48"/>
+    <mergeCell ref="K48:N48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11569AFC-E450-9947-95BA-0EAD5E7E5320}">
+  <dimension ref="B1:H23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="5">
+        <v>22</v>
+      </c>
+      <c r="D2" s="5">
+        <v>23</v>
+      </c>
+      <c r="E2" s="5">
+        <v>24</v>
+      </c>
+      <c r="F2" s="5">
+        <v>25</v>
+      </c>
+      <c r="G2" s="5">
+        <v>26</v>
+      </c>
+      <c r="H2" s="6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B3" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="21">
+        <v>0.30944899999999997</v>
+      </c>
+      <c r="D3" s="21">
+        <v>0.580986</v>
+      </c>
+      <c r="E3" s="21">
+        <v>1.1536900000000001</v>
+      </c>
+      <c r="F3" s="21">
+        <v>1.981185</v>
+      </c>
+      <c r="G3" s="21">
+        <v>4.0958680000000003</v>
+      </c>
+      <c r="H3" s="50">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B4" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="21">
+        <v>0.40713100000000002</v>
+      </c>
+      <c r="D4" s="21">
+        <v>0.665489</v>
+      </c>
+      <c r="E4" s="21">
+        <v>0.70998700000000003</v>
+      </c>
+      <c r="F4" s="21">
+        <v>1.2236100000000001</v>
+      </c>
+      <c r="G4" s="21">
+        <v>1.3767259999999999</v>
+      </c>
+      <c r="H4" s="50">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B5" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="21">
+        <v>49.74</v>
+      </c>
+      <c r="D5" s="21">
+        <v>54.15</v>
+      </c>
+      <c r="E5" s="21">
+        <v>53.96</v>
+      </c>
+      <c r="F5" s="21">
+        <v>58.43</v>
+      </c>
+      <c r="G5" s="21">
+        <v>57.96</v>
+      </c>
+      <c r="H5" s="50">
+        <v>62.11</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="25">
+        <v>2.8056999999999999E-2</v>
+      </c>
+      <c r="D6" s="25">
+        <v>3.0529000000000001E-2</v>
+      </c>
+      <c r="E6" s="25">
+        <v>3.0529000000000001E-2</v>
+      </c>
+      <c r="F6" s="25">
+        <v>3.3001000000000003E-2</v>
+      </c>
+      <c r="G6" s="25">
+        <v>3.3001000000000003E-2</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="5">
+        <v>22</v>
+      </c>
+      <c r="D10" s="5">
+        <v>23</v>
+      </c>
+      <c r="E10" s="5">
+        <v>24</v>
+      </c>
+      <c r="F10" s="5">
+        <v>25</v>
+      </c>
+      <c r="G10" s="6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B11" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="21">
+        <v>0.64</v>
+      </c>
+      <c r="D11" s="21">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="E11" s="21">
+        <v>2.27</v>
+      </c>
+      <c r="F11" s="21">
+        <v>3.87</v>
+      </c>
+      <c r="G11" s="24">
+        <v>7.97</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B12" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="21">
+        <v>0.43</v>
+      </c>
+      <c r="D12" s="21">
+        <v>0.71</v>
+      </c>
+      <c r="E12" s="21">
+        <v>0.75</v>
+      </c>
+      <c r="F12" s="21">
+        <v>1.29</v>
+      </c>
+      <c r="G12" s="24">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B13" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="21">
+        <v>49.97</v>
+      </c>
+      <c r="D13" s="21">
+        <v>54.13</v>
+      </c>
+      <c r="E13" s="21">
+        <v>54.28</v>
+      </c>
+      <c r="F13" s="21">
+        <v>58.35</v>
+      </c>
+      <c r="G13" s="24">
+        <v>58.35</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="25">
+        <v>2.8056999999999999E-2</v>
+      </c>
+      <c r="D14" s="25">
+        <v>3.0529000000000001E-2</v>
+      </c>
+      <c r="E14" s="25">
+        <v>3.0529000000000001E-2</v>
+      </c>
+      <c r="F14" s="25">
+        <v>3.3001000000000003E-2</v>
+      </c>
+      <c r="G14" s="26">
+        <v>3.3001000000000003E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="5">
+        <v>22</v>
+      </c>
+      <c r="D19" s="5">
+        <v>23</v>
+      </c>
+      <c r="E19" s="5">
+        <v>24</v>
+      </c>
+      <c r="F19" s="5">
+        <v>25</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B20" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="21">
+        <v>1.4759340000000001</v>
+      </c>
+      <c r="D20" s="21">
+        <v>3.0387550000000001</v>
+      </c>
+      <c r="E20" s="21">
+        <v>6.3517390000000002</v>
+      </c>
+      <c r="F20" s="21">
+        <v>13.625584999999999</v>
+      </c>
+      <c r="G20" s="24">
+        <f>F20*2</f>
+        <v>27.251169999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B21" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="21">
+        <v>3.6002700000000001</v>
+      </c>
+      <c r="D21" s="21">
+        <v>8.1892750000000003</v>
+      </c>
+      <c r="E21" s="21">
+        <v>18.139723</v>
+      </c>
+      <c r="F21" s="21">
+        <v>44.545726999999999</v>
+      </c>
+      <c r="G21" s="24">
+        <f t="shared" ref="G21:G23" si="0">F21*2</f>
+        <v>89.091453999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B22" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="21">
+        <v>0.71473600000000004</v>
+      </c>
+      <c r="D22" s="21">
+        <v>0.901111</v>
+      </c>
+      <c r="E22" s="21">
+        <v>1.3074030000000001</v>
+      </c>
+      <c r="F22" s="21">
+        <v>1.6227499999999999</v>
+      </c>
+      <c r="G22" s="24">
+        <f t="shared" si="0"/>
+        <v>3.2454999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B23" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="25">
+        <v>1.225517</v>
+      </c>
+      <c r="D23" s="25">
+        <v>1.3273010000000001</v>
+      </c>
+      <c r="E23" s="25">
+        <v>1.4331130000000001</v>
+      </c>
+      <c r="F23" s="25">
+        <v>1.542953</v>
+      </c>
+      <c r="G23" s="24">
+        <f t="shared" si="0"/>
+        <v>3.085906</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD2CA5C5-CBB8-F941-9958-E8BE692DEF95}">
   <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -6249,2225 +6978,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11569AFC-E450-9947-95BA-0EAD5E7E5320}">
-  <dimension ref="B1:H23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="5">
-        <v>22</v>
-      </c>
-      <c r="D2" s="5">
-        <v>23</v>
-      </c>
-      <c r="E2" s="5">
-        <v>24</v>
-      </c>
-      <c r="F2" s="5">
-        <v>25</v>
-      </c>
-      <c r="G2" s="5">
-        <v>26</v>
-      </c>
-      <c r="H2" s="6">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B3" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="21">
-        <v>0.30944899999999997</v>
-      </c>
-      <c r="D3" s="21">
-        <v>0.580986</v>
-      </c>
-      <c r="E3" s="21">
-        <v>1.1536900000000001</v>
-      </c>
-      <c r="F3" s="21">
-        <v>1.981185</v>
-      </c>
-      <c r="G3" s="21">
-        <v>4.0958680000000003</v>
-      </c>
-      <c r="H3" s="52">
-        <v>6.77</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B4" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="21">
-        <v>0.40713100000000002</v>
-      </c>
-      <c r="D4" s="21">
-        <v>0.665489</v>
-      </c>
-      <c r="E4" s="21">
-        <v>0.70998700000000003</v>
-      </c>
-      <c r="F4" s="21">
-        <v>1.2236100000000001</v>
-      </c>
-      <c r="G4" s="21">
-        <v>1.3767259999999999</v>
-      </c>
-      <c r="H4" s="52">
-        <v>2.48</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B5" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="21">
-        <v>49.74</v>
-      </c>
-      <c r="D5" s="21">
-        <v>54.15</v>
-      </c>
-      <c r="E5" s="21">
-        <v>53.96</v>
-      </c>
-      <c r="F5" s="21">
-        <v>58.43</v>
-      </c>
-      <c r="G5" s="21">
-        <v>57.96</v>
-      </c>
-      <c r="H5" s="52">
-        <v>62.11</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B6" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="25">
-        <v>2.8056999999999999E-2</v>
-      </c>
-      <c r="D6" s="25">
-        <v>3.0529000000000001E-2</v>
-      </c>
-      <c r="E6" s="25">
-        <v>3.0529000000000001E-2</v>
-      </c>
-      <c r="F6" s="25">
-        <v>3.3001000000000003E-2</v>
-      </c>
-      <c r="G6" s="25">
-        <v>3.3001000000000003E-2</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="5">
-        <v>22</v>
-      </c>
-      <c r="D10" s="5">
-        <v>23</v>
-      </c>
-      <c r="E10" s="5">
-        <v>24</v>
-      </c>
-      <c r="F10" s="5">
-        <v>25</v>
-      </c>
-      <c r="G10" s="6">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="21">
-        <v>0.64</v>
-      </c>
-      <c r="D11" s="21">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="E11" s="21">
-        <v>2.27</v>
-      </c>
-      <c r="F11" s="21">
-        <v>3.87</v>
-      </c>
-      <c r="G11" s="24">
-        <v>7.97</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B12" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="21">
-        <v>0.43</v>
-      </c>
-      <c r="D12" s="21">
-        <v>0.71</v>
-      </c>
-      <c r="E12" s="21">
-        <v>0.75</v>
-      </c>
-      <c r="F12" s="21">
-        <v>1.29</v>
-      </c>
-      <c r="G12" s="24">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="21">
-        <v>49.97</v>
-      </c>
-      <c r="D13" s="21">
-        <v>54.13</v>
-      </c>
-      <c r="E13" s="21">
-        <v>54.28</v>
-      </c>
-      <c r="F13" s="21">
-        <v>58.35</v>
-      </c>
-      <c r="G13" s="24">
-        <v>58.35</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="25">
-        <v>2.8056999999999999E-2</v>
-      </c>
-      <c r="D14" s="25">
-        <v>3.0529000000000001E-2</v>
-      </c>
-      <c r="E14" s="25">
-        <v>3.0529000000000001E-2</v>
-      </c>
-      <c r="F14" s="25">
-        <v>3.3001000000000003E-2</v>
-      </c>
-      <c r="G14" s="26">
-        <v>3.3001000000000003E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="5">
-        <v>22</v>
-      </c>
-      <c r="D19" s="5">
-        <v>23</v>
-      </c>
-      <c r="E19" s="5">
-        <v>24</v>
-      </c>
-      <c r="F19" s="5">
-        <v>25</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="21">
-        <v>1.4759340000000001</v>
-      </c>
-      <c r="D20" s="21">
-        <v>3.0387550000000001</v>
-      </c>
-      <c r="E20" s="21">
-        <v>6.3517390000000002</v>
-      </c>
-      <c r="F20" s="21">
-        <v>13.625584999999999</v>
-      </c>
-      <c r="G20" s="24">
-        <f>F20*2</f>
-        <v>27.251169999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="21">
-        <v>3.6002700000000001</v>
-      </c>
-      <c r="D21" s="21">
-        <v>8.1892750000000003</v>
-      </c>
-      <c r="E21" s="21">
-        <v>18.139723</v>
-      </c>
-      <c r="F21" s="21">
-        <v>44.545726999999999</v>
-      </c>
-      <c r="G21" s="24">
-        <f t="shared" ref="G21:G23" si="0">F21*2</f>
-        <v>89.091453999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="21">
-        <v>0.71473600000000004</v>
-      </c>
-      <c r="D22" s="21">
-        <v>0.901111</v>
-      </c>
-      <c r="E22" s="21">
-        <v>1.3074030000000001</v>
-      </c>
-      <c r="F22" s="21">
-        <v>1.6227499999999999</v>
-      </c>
-      <c r="G22" s="24">
-        <f t="shared" si="0"/>
-        <v>3.2454999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="25">
-        <v>1.225517</v>
-      </c>
-      <c r="D23" s="25">
-        <v>1.3273010000000001</v>
-      </c>
-      <c r="E23" s="25">
-        <v>1.4331130000000001</v>
-      </c>
-      <c r="F23" s="25">
-        <v>1.542953</v>
-      </c>
-      <c r="G23" s="24">
-        <f t="shared" si="0"/>
-        <v>3.085906</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10F5213-1942-4945-915F-4EC6808BC28C}">
-  <dimension ref="A4:X55"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="8.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="6.6640625" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" customWidth="1"/>
-    <col min="6" max="6" width="7" customWidth="1"/>
-    <col min="7" max="7" width="8.5" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="8.1640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="B4" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="P4" s="15"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="B5" s="38"/>
-      <c r="C5" s="38" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="38">
-        <v>728</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="38">
-        <v>4</v>
-      </c>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A7" s="59"/>
-      <c r="B7" s="59" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59"/>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59"/>
-      <c r="N7" s="59"/>
-      <c r="O7" s="59"/>
-      <c r="P7" s="59"/>
-      <c r="Q7" s="59"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="31"/>
-      <c r="T7" s="59"/>
-      <c r="U7" s="59"/>
-      <c r="V7" s="59"/>
-      <c r="W7" s="59"/>
-      <c r="X7" s="59"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A8" s="59"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="60" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60" t="s">
-        <v>91</v>
-      </c>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60" t="s">
-        <v>92</v>
-      </c>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
-      <c r="N8" s="60"/>
-      <c r="O8" s="59"/>
-      <c r="P8" s="59"/>
-      <c r="Q8" s="59"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="31"/>
-      <c r="T8" s="59"/>
-      <c r="U8" s="59"/>
-      <c r="V8" s="59"/>
-      <c r="W8" s="59"/>
-      <c r="X8" s="59"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A9" s="59"/>
-      <c r="B9" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="62" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" s="63" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="63" t="s">
-        <v>84</v>
-      </c>
-      <c r="F9" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="G9" s="63" t="s">
-        <v>87</v>
-      </c>
-      <c r="H9" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="I9" s="63" t="s">
-        <v>89</v>
-      </c>
-      <c r="J9" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="K9" s="63" t="s">
-        <v>93</v>
-      </c>
-      <c r="L9" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="M9" s="63" t="s">
-        <v>89</v>
-      </c>
-      <c r="N9" s="64" t="s">
-        <v>95</v>
-      </c>
-      <c r="O9" s="59"/>
-      <c r="P9" s="59"/>
-      <c r="Q9" s="59"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="31"/>
-      <c r="T9" s="59"/>
-      <c r="U9" s="59"/>
-      <c r="V9" s="59"/>
-      <c r="W9" s="59"/>
-      <c r="X9" s="59"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A10" s="59"/>
-      <c r="B10" s="65" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="31">
-        <v>3.5100000000000002</v>
-      </c>
-      <c r="D10" s="31">
-        <v>0.61199999999999988</v>
-      </c>
-      <c r="E10" s="31">
-        <v>17.436</v>
-      </c>
-      <c r="F10" s="31">
-        <v>2.8980000000000001</v>
-      </c>
-      <c r="G10" s="31">
-        <v>224.24</v>
-      </c>
-      <c r="H10" s="31">
-        <v>222.81</v>
-      </c>
-      <c r="I10" s="31">
-        <v>99.36</v>
-      </c>
-      <c r="J10" s="31">
-        <v>1.4300000000000002</v>
-      </c>
-      <c r="K10" s="31">
-        <v>135.44881000000004</v>
-      </c>
-      <c r="L10" s="31">
-        <v>135.27241000000001</v>
-      </c>
-      <c r="M10" s="31">
-        <v>99.87</v>
-      </c>
-      <c r="N10" s="31">
-        <v>0.17641000000000004</v>
-      </c>
-      <c r="O10" s="59"/>
-      <c r="P10" s="59"/>
-      <c r="Q10" s="59"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="59"/>
-      <c r="U10" s="59"/>
-      <c r="V10" s="59"/>
-      <c r="W10" s="59"/>
-      <c r="X10" s="59"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A11" s="59"/>
-      <c r="B11" s="65">
-        <v>1</v>
-      </c>
-      <c r="C11" s="66">
-        <v>3.38</v>
-      </c>
-      <c r="D11" s="59">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="E11" s="59">
-        <v>16.78</v>
-      </c>
-      <c r="F11" s="59">
-        <v>2.81</v>
-      </c>
-      <c r="G11" s="59">
-        <v>204.04</v>
-      </c>
-      <c r="H11" s="59">
-        <v>203.81</v>
-      </c>
-      <c r="I11" s="59">
-        <v>99.89</v>
-      </c>
-      <c r="J11" s="59">
-        <v>0.23</v>
-      </c>
-      <c r="K11" s="31">
-        <v>90.9</v>
-      </c>
-      <c r="L11" s="31">
-        <v>90.892229080200195</v>
-      </c>
-      <c r="M11" s="31">
-        <v>99.99</v>
-      </c>
-      <c r="N11" s="67">
-        <v>9.6464157104492101E-3</v>
-      </c>
-      <c r="O11" s="59"/>
-      <c r="P11" s="68"/>
-      <c r="Q11" s="59"/>
-      <c r="R11" s="68"/>
-      <c r="S11" s="68"/>
-      <c r="T11" s="59"/>
-      <c r="U11" s="59"/>
-      <c r="V11" s="59"/>
-      <c r="W11" s="59"/>
-      <c r="X11" s="59"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A12" s="59"/>
-      <c r="B12" s="65">
-        <v>2</v>
-      </c>
-      <c r="C12" s="66">
-        <v>6.36</v>
-      </c>
-      <c r="D12" s="59">
-        <v>1.01</v>
-      </c>
-      <c r="E12" s="59">
-        <v>15.94</v>
-      </c>
-      <c r="F12" s="59">
-        <v>5.35</v>
-      </c>
-      <c r="G12" s="59">
-        <v>300.81</v>
-      </c>
-      <c r="H12" s="59">
-        <v>300.55</v>
-      </c>
-      <c r="I12" s="59">
-        <v>99.91</v>
-      </c>
-      <c r="J12" s="59">
-        <v>0.26</v>
-      </c>
-      <c r="K12" s="31">
-        <v>117.72</v>
-      </c>
-      <c r="L12" s="31">
-        <v>117.7</v>
-      </c>
-      <c r="M12" s="31">
-        <v>99.99</v>
-      </c>
-      <c r="N12" s="67">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="O12" s="59"/>
-      <c r="P12" s="59"/>
-      <c r="Q12" s="59"/>
-      <c r="R12" s="68"/>
-      <c r="S12" s="68"/>
-      <c r="T12" s="59"/>
-      <c r="U12" s="59"/>
-      <c r="V12" s="59"/>
-      <c r="W12" s="59"/>
-      <c r="X12" s="59"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A13" s="59"/>
-      <c r="B13" s="65">
-        <v>4</v>
-      </c>
-      <c r="C13" s="66">
-        <v>14.16</v>
-      </c>
-      <c r="D13" s="59">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="E13" s="59">
-        <v>15.82</v>
-      </c>
-      <c r="F13" s="59">
-        <v>11.92</v>
-      </c>
-      <c r="G13" s="59">
-        <v>382.74</v>
-      </c>
-      <c r="H13" s="59">
-        <v>382.45</v>
-      </c>
-      <c r="I13" s="59">
-        <v>99.92</v>
-      </c>
-      <c r="J13" s="59">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="K13" s="31">
-        <v>136.86000000000001</v>
-      </c>
-      <c r="L13" s="31">
-        <v>136.84</v>
-      </c>
-      <c r="M13" s="31">
-        <v>99.99</v>
-      </c>
-      <c r="N13" s="67">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O13" s="59"/>
-      <c r="P13" s="59"/>
-      <c r="Q13" s="59"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="31"/>
-      <c r="T13" s="59"/>
-      <c r="U13" s="59"/>
-      <c r="V13" s="59"/>
-      <c r="W13" s="59"/>
-      <c r="X13" s="59"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A14" s="59"/>
-      <c r="B14" s="65">
-        <v>8</v>
-      </c>
-      <c r="C14" s="66">
-        <v>29.51</v>
-      </c>
-      <c r="D14" s="59">
-        <v>4.66</v>
-      </c>
-      <c r="E14" s="59">
-        <v>15.81</v>
-      </c>
-      <c r="F14" s="59">
-        <v>24.84</v>
-      </c>
-      <c r="G14" s="59">
-        <v>566.41</v>
-      </c>
-      <c r="H14" s="59">
-        <v>566.09</v>
-      </c>
-      <c r="I14" s="59">
-        <v>99.94</v>
-      </c>
-      <c r="J14" s="59">
-        <v>0.31</v>
-      </c>
-      <c r="K14" s="31">
-        <v>183.081004142761</v>
-      </c>
-      <c r="L14" s="31">
-        <v>183.05876731872499</v>
-      </c>
-      <c r="M14" s="59">
-        <v>99.99</v>
-      </c>
-      <c r="N14" s="67">
-        <v>2.22368240356445E-2</v>
-      </c>
-      <c r="O14" s="59"/>
-      <c r="P14" s="59"/>
-      <c r="Q14" s="59"/>
-      <c r="R14" s="31"/>
-      <c r="S14" s="31"/>
-      <c r="T14" s="59"/>
-      <c r="U14" s="59"/>
-      <c r="V14" s="59"/>
-      <c r="W14" s="59"/>
-      <c r="X14" s="59"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A15" s="59"/>
-      <c r="B15" s="69">
-        <v>16</v>
-      </c>
-      <c r="C15" s="70">
-        <v>92.12</v>
-      </c>
-      <c r="D15" s="71">
-        <v>23.85</v>
-      </c>
-      <c r="E15" s="71">
-        <v>25.89</v>
-      </c>
-      <c r="F15" s="71">
-        <v>68.27</v>
-      </c>
-      <c r="G15" s="71">
-        <v>968.41</v>
-      </c>
-      <c r="H15" s="71">
-        <v>967.77</v>
-      </c>
-      <c r="I15" s="71">
-        <v>99.93</v>
-      </c>
-      <c r="J15" s="71">
-        <v>0.64</v>
-      </c>
-      <c r="K15" s="71">
-        <v>220.75</v>
-      </c>
-      <c r="L15" s="71">
-        <v>220.72</v>
-      </c>
-      <c r="M15" s="71">
-        <v>99.98</v>
-      </c>
-      <c r="N15" s="72">
-        <v>0.04</v>
-      </c>
-      <c r="O15" s="59"/>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="59"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
-      <c r="T15" s="59"/>
-      <c r="U15" s="59"/>
-      <c r="V15" s="59"/>
-      <c r="W15" s="59"/>
-      <c r="X15" s="59"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A16" s="59"/>
-      <c r="B16" s="59">
-        <v>32</v>
-      </c>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="59"/>
-      <c r="I16" s="59"/>
-      <c r="J16" s="59"/>
-      <c r="K16" s="59"/>
-      <c r="L16" s="59"/>
-      <c r="M16" s="59"/>
-      <c r="N16" s="59"/>
-      <c r="O16" s="59"/>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="59"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="31"/>
-      <c r="T16" s="59"/>
-      <c r="U16" s="59"/>
-      <c r="V16" s="59"/>
-      <c r="W16" s="59"/>
-      <c r="X16" s="59"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A17" s="59"/>
-      <c r="B17" s="59">
-        <v>64</v>
-      </c>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="59"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="59"/>
-      <c r="L17" s="59"/>
-      <c r="M17" s="59"/>
-      <c r="N17" s="59"/>
-      <c r="O17" s="59"/>
-      <c r="P17" s="59"/>
-      <c r="Q17" s="59"/>
-      <c r="R17" s="59"/>
-      <c r="S17" s="59"/>
-      <c r="T17" s="59"/>
-      <c r="U17" s="59"/>
-      <c r="V17" s="59"/>
-      <c r="W17" s="59"/>
-      <c r="X17" s="59"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A18" s="59"/>
-      <c r="B18" s="59">
-        <v>128</v>
-      </c>
-      <c r="C18" s="59"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="59"/>
-      <c r="I18" s="59"/>
-      <c r="J18" s="59"/>
-      <c r="K18" s="59"/>
-      <c r="L18" s="59"/>
-      <c r="M18" s="59"/>
-      <c r="N18" s="59"/>
-      <c r="O18" s="59"/>
-      <c r="P18" s="59"/>
-      <c r="Q18" s="59"/>
-      <c r="R18" s="59"/>
-      <c r="S18" s="59"/>
-      <c r="T18" s="59"/>
-      <c r="U18" s="59"/>
-      <c r="V18" s="59"/>
-      <c r="W18" s="59"/>
-      <c r="X18" s="59"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A19" s="59"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="59"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="59"/>
-      <c r="L19" s="59"/>
-      <c r="M19" s="59"/>
-      <c r="N19" s="59"/>
-      <c r="O19" s="59"/>
-      <c r="P19" s="59"/>
-      <c r="Q19" s="59"/>
-      <c r="R19" s="59"/>
-      <c r="S19" s="59"/>
-      <c r="T19" s="59"/>
-      <c r="U19" s="59"/>
-      <c r="V19" s="59"/>
-      <c r="W19" s="59"/>
-      <c r="X19" s="59"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A20" s="59"/>
-      <c r="B20" s="59"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="59"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="59"/>
-      <c r="L20" s="59"/>
-      <c r="M20" s="59"/>
-      <c r="N20" s="59"/>
-      <c r="O20" s="59"/>
-      <c r="P20" s="59"/>
-      <c r="Q20" s="59"/>
-      <c r="R20" s="59"/>
-      <c r="S20" s="59"/>
-      <c r="T20" s="59"/>
-      <c r="U20" s="59"/>
-      <c r="V20" s="59"/>
-      <c r="W20" s="59"/>
-      <c r="X20" s="59"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A21" s="59"/>
-      <c r="B21" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="59"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="59"/>
-      <c r="L21" s="59"/>
-      <c r="M21" s="59"/>
-      <c r="N21" s="59"/>
-      <c r="O21" s="59"/>
-      <c r="P21" s="59"/>
-      <c r="Q21" s="59"/>
-      <c r="R21" s="59"/>
-      <c r="S21" s="59"/>
-      <c r="T21" s="59"/>
-      <c r="U21" s="59"/>
-      <c r="V21" s="59"/>
-      <c r="W21" s="59"/>
-      <c r="X21" s="59"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A22" s="59"/>
-      <c r="B22" s="59"/>
-      <c r="C22" s="60" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60" t="s">
-        <v>91</v>
-      </c>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="60" t="s">
-        <v>92</v>
-      </c>
-      <c r="L22" s="60"/>
-      <c r="M22" s="60"/>
-      <c r="N22" s="60"/>
-      <c r="O22" s="59"/>
-      <c r="P22" s="59" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q22" s="59" t="s">
-        <v>106</v>
-      </c>
-      <c r="R22" s="59"/>
-      <c r="S22" s="59"/>
-      <c r="T22" s="59"/>
-      <c r="U22" s="59"/>
-      <c r="V22" s="59"/>
-      <c r="W22" s="59"/>
-      <c r="X22" s="59"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A23" s="59" t="s">
-        <v>112</v>
-      </c>
-      <c r="B23" s="61" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" s="62" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" s="63" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" s="63" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="G23" s="63" t="s">
-        <v>87</v>
-      </c>
-      <c r="H23" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="I23" s="63" t="s">
-        <v>89</v>
-      </c>
-      <c r="J23" s="63" t="s">
-        <v>90</v>
-      </c>
-      <c r="K23" s="63" t="s">
-        <v>93</v>
-      </c>
-      <c r="L23" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="M23" s="63" t="s">
-        <v>89</v>
-      </c>
-      <c r="N23" s="64" t="s">
-        <v>95</v>
-      </c>
-      <c r="O23" s="59"/>
-      <c r="P23" s="62" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q23" s="63">
-        <v>22</v>
-      </c>
-      <c r="R23" s="63">
-        <v>23</v>
-      </c>
-      <c r="S23" s="63">
-        <v>24</v>
-      </c>
-      <c r="T23" s="63">
-        <v>25</v>
-      </c>
-      <c r="U23" s="63">
-        <v>26</v>
-      </c>
-      <c r="V23" s="63">
-        <v>27</v>
-      </c>
-      <c r="W23" s="64">
-        <v>28</v>
-      </c>
-      <c r="X23" s="59"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A24" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="B24" s="65" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" s="73">
-        <v>5.4716640000000005</v>
-      </c>
-      <c r="D24" s="31">
-        <v>2.573664</v>
-      </c>
-      <c r="E24" s="31">
-        <v>47.036221522374177</v>
-      </c>
-      <c r="F24" s="31">
-        <v>2.8980000000000001</v>
-      </c>
-      <c r="G24" s="31">
-        <v>109.35000000000001</v>
-      </c>
-      <c r="H24" s="31">
-        <v>107.92</v>
-      </c>
-      <c r="I24" s="31">
-        <v>98.692272519433004</v>
-      </c>
-      <c r="J24" s="31">
-        <v>1.4300000000000002</v>
-      </c>
-      <c r="K24" s="31">
-        <v>0.23746800000000004</v>
-      </c>
-      <c r="L24" s="31">
-        <v>6.1058000000000001E-2</v>
-      </c>
-      <c r="M24" s="31">
-        <v>25.712095945558978</v>
-      </c>
-      <c r="N24" s="67">
-        <v>0.17641000000000004</v>
-      </c>
-      <c r="O24" s="59"/>
-      <c r="P24" s="66" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q24" s="31">
-        <v>0.30944899999999997</v>
-      </c>
-      <c r="R24" s="31">
-        <v>0.580986</v>
-      </c>
-      <c r="S24" s="31">
-        <v>1.1536900000000001</v>
-      </c>
-      <c r="T24" s="31">
-        <v>1.981185</v>
-      </c>
-      <c r="U24" s="31">
-        <v>4.0958680000000003</v>
-      </c>
-      <c r="V24" s="59">
-        <v>6.77</v>
-      </c>
-      <c r="W24" s="74">
-        <v>13.69</v>
-      </c>
-      <c r="X24" s="59"/>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A25" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="B25" s="65">
-        <v>1</v>
-      </c>
-      <c r="C25" s="73">
-        <f>D25+F25</f>
-        <v>5.3836639999999996</v>
-      </c>
-      <c r="D25" s="31">
-        <v>2.573664</v>
-      </c>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59">
-        <v>2.81</v>
-      </c>
-      <c r="G25" s="31">
-        <f>H25+J25</f>
-        <v>108.15</v>
-      </c>
-      <c r="H25" s="31">
-        <v>107.92</v>
-      </c>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59">
-        <v>0.23</v>
-      </c>
-      <c r="K25" s="31">
-        <f>L25+N25</f>
-        <v>7.0704415710449206E-2</v>
-      </c>
-      <c r="L25" s="31">
-        <v>6.1058000000000001E-2</v>
-      </c>
-      <c r="M25" s="31"/>
-      <c r="N25" s="67">
-        <v>9.6464157104492101E-3</v>
-      </c>
-      <c r="O25" s="59"/>
-      <c r="P25" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q25" s="31">
-        <v>0.40713100000000002</v>
-      </c>
-      <c r="R25" s="31">
-        <v>0.665489</v>
-      </c>
-      <c r="S25" s="31">
-        <v>0.70998700000000003</v>
-      </c>
-      <c r="T25" s="31">
-        <v>1.2236100000000001</v>
-      </c>
-      <c r="U25" s="31">
-        <v>1.3767259999999999</v>
-      </c>
-      <c r="V25" s="59">
-        <v>2.48</v>
-      </c>
-      <c r="W25" s="74">
-        <v>2.92</v>
-      </c>
-      <c r="X25" s="59"/>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A26" s="59" t="s">
-        <v>113</v>
-      </c>
-      <c r="B26" s="65">
-        <v>2</v>
-      </c>
-      <c r="C26" s="73">
-        <f t="shared" ref="C26:C29" si="0">D26+F26</f>
-        <v>9.7784049999999993</v>
-      </c>
-      <c r="D26" s="59">
-        <f>T24+T25*2</f>
-        <v>4.4284049999999997</v>
-      </c>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59">
-        <v>5.35</v>
-      </c>
-      <c r="G26" s="31">
-        <f t="shared" ref="G26:G29" si="1">H26+J26</f>
-        <v>117.12</v>
-      </c>
-      <c r="H26" s="59">
-        <f>T26*2</f>
-        <v>116.86</v>
-      </c>
-      <c r="I26" s="59"/>
-      <c r="J26" s="59">
-        <v>0.26</v>
-      </c>
-      <c r="K26" s="31">
-        <f t="shared" ref="K26:K29" si="2">L26+N26</f>
-        <v>7.7002000000000001E-2</v>
-      </c>
-      <c r="L26" s="31">
-        <f>T27*2</f>
-        <v>6.6002000000000005E-2</v>
-      </c>
-      <c r="M26" s="31"/>
-      <c r="N26" s="67">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="O26" s="59"/>
-      <c r="P26" s="66" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q26" s="31">
-        <v>49.74</v>
-      </c>
-      <c r="R26" s="31">
-        <v>54.15</v>
-      </c>
-      <c r="S26" s="31">
-        <v>53.96</v>
-      </c>
-      <c r="T26" s="31">
-        <v>58.43</v>
-      </c>
-      <c r="U26" s="31">
-        <v>57.96</v>
-      </c>
-      <c r="V26" s="59">
-        <v>62.11</v>
-      </c>
-      <c r="W26" s="74">
-        <v>61.83</v>
-      </c>
-      <c r="X26" s="59"/>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A27" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="B27" s="65">
-        <v>4</v>
-      </c>
-      <c r="C27" s="73">
-        <f t="shared" si="0"/>
-        <v>18.76932</v>
-      </c>
-      <c r="D27" s="59">
-        <f>U24+U25*2</f>
-        <v>6.8493200000000005</v>
-      </c>
-      <c r="E27" s="59"/>
-      <c r="F27" s="59">
-        <v>11.92</v>
-      </c>
-      <c r="G27" s="31">
-        <f t="shared" si="1"/>
-        <v>116.21000000000001</v>
-      </c>
-      <c r="H27" s="59">
-        <f>U26*2</f>
-        <v>115.92</v>
-      </c>
-      <c r="I27" s="59"/>
-      <c r="J27" s="59">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="K27" s="31">
-        <f t="shared" si="2"/>
-        <v>8.1002000000000005E-2</v>
-      </c>
-      <c r="L27" s="31">
-        <f>U27*2</f>
-        <v>6.6002000000000005E-2</v>
-      </c>
-      <c r="M27" s="31"/>
-      <c r="N27" s="67">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O27" s="59"/>
-      <c r="P27" s="70" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q27" s="75">
-        <v>2.8056999999999999E-2</v>
-      </c>
-      <c r="R27" s="75">
-        <v>3.0529000000000001E-2</v>
-      </c>
-      <c r="S27" s="75">
-        <v>3.0529000000000001E-2</v>
-      </c>
-      <c r="T27" s="75">
-        <v>3.3001000000000003E-2</v>
-      </c>
-      <c r="U27" s="75">
-        <v>3.3001000000000003E-2</v>
-      </c>
-      <c r="V27" s="71">
-        <v>0.04</v>
-      </c>
-      <c r="W27" s="72">
-        <v>0.04</v>
-      </c>
-      <c r="X27" s="59"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A28" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="B28" s="65">
-        <v>8</v>
-      </c>
-      <c r="C28" s="73">
-        <f t="shared" si="0"/>
-        <v>36.57</v>
-      </c>
-      <c r="D28" s="59">
-        <f>V24+V25*2</f>
-        <v>11.73</v>
-      </c>
-      <c r="E28" s="59"/>
-      <c r="F28" s="59">
-        <v>24.84</v>
-      </c>
-      <c r="G28" s="31">
-        <f t="shared" si="1"/>
-        <v>124.53</v>
-      </c>
-      <c r="H28" s="59">
-        <f>V26*2</f>
-        <v>124.22</v>
-      </c>
-      <c r="I28" s="59"/>
-      <c r="J28" s="59">
-        <v>0.31</v>
-      </c>
-      <c r="K28" s="31">
-        <f t="shared" si="2"/>
-        <v>0.10223682403564451</v>
-      </c>
-      <c r="L28" s="31">
-        <f>V27*2</f>
-        <v>0.08</v>
-      </c>
-      <c r="M28" s="59"/>
-      <c r="N28" s="67">
-        <v>2.22368240356445E-2</v>
-      </c>
-      <c r="O28" s="59"/>
-      <c r="P28" s="59"/>
-      <c r="Q28" s="59"/>
-      <c r="R28" s="59"/>
-      <c r="S28" s="59"/>
-      <c r="T28" s="59"/>
-      <c r="U28" s="59"/>
-      <c r="V28" s="59"/>
-      <c r="W28" s="59"/>
-      <c r="X28" s="59"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A29" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="B29" s="69">
-        <v>16</v>
-      </c>
-      <c r="C29" s="73">
-        <f t="shared" si="0"/>
-        <v>87.8</v>
-      </c>
-      <c r="D29" s="71">
-        <f>W24+W25*2</f>
-        <v>19.53</v>
-      </c>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71">
-        <v>68.27</v>
-      </c>
-      <c r="G29" s="31">
-        <f t="shared" si="1"/>
-        <v>124.3</v>
-      </c>
-      <c r="H29" s="71">
-        <f>W26*2</f>
-        <v>123.66</v>
-      </c>
-      <c r="I29" s="71"/>
-      <c r="J29" s="71">
-        <v>0.64</v>
-      </c>
-      <c r="K29" s="31">
-        <f t="shared" si="2"/>
-        <v>0.12</v>
-      </c>
-      <c r="L29" s="71">
-        <f>W27*2</f>
-        <v>0.08</v>
-      </c>
-      <c r="M29" s="71"/>
-      <c r="N29" s="72">
-        <v>0.04</v>
-      </c>
-      <c r="O29" s="59"/>
-      <c r="P29" s="59"/>
-      <c r="Q29" s="59"/>
-      <c r="R29" s="59"/>
-      <c r="S29" s="59"/>
-      <c r="T29" s="59"/>
-      <c r="U29" s="59"/>
-      <c r="V29" s="59"/>
-      <c r="W29" s="59"/>
-      <c r="X29" s="59"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A30" s="59"/>
-      <c r="B30" s="59"/>
-      <c r="C30" s="59"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="59"/>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-      <c r="I30" s="59"/>
-      <c r="J30" s="59"/>
-      <c r="K30" s="59"/>
-      <c r="L30" s="59"/>
-      <c r="M30" s="59"/>
-      <c r="N30" s="59"/>
-      <c r="O30" s="59"/>
-      <c r="P30" s="59"/>
-      <c r="Q30" s="59"/>
-      <c r="R30" s="59"/>
-      <c r="S30" s="59"/>
-      <c r="T30" s="59"/>
-      <c r="U30" s="59"/>
-      <c r="V30" s="59"/>
-      <c r="W30" s="59"/>
-      <c r="X30" s="59"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A31" s="59"/>
-      <c r="B31" s="59"/>
-      <c r="C31" s="59"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="59"/>
-      <c r="J31" s="59"/>
-      <c r="K31" s="59"/>
-      <c r="L31" s="59"/>
-      <c r="M31" s="59"/>
-      <c r="N31" s="59"/>
-      <c r="O31" s="59"/>
-      <c r="P31" s="59"/>
-      <c r="Q31" s="59"/>
-      <c r="R31" s="59"/>
-      <c r="S31" s="59"/>
-      <c r="T31" s="59"/>
-      <c r="U31" s="59"/>
-      <c r="V31" s="59"/>
-      <c r="W31" s="59"/>
-      <c r="X31" s="59"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C34" s="14"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C35" s="58" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58" t="s">
-        <v>91</v>
-      </c>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="58"/>
-      <c r="K35" s="58" t="s">
-        <v>92</v>
-      </c>
-      <c r="L35" s="58"/>
-      <c r="M35" s="58"/>
-      <c r="N35" s="58"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B36" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G36" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="I36" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="L36" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="M36" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="N36" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="46" t="s">
-        <v>109</v>
-      </c>
-      <c r="C37" s="21">
-        <v>3.5100000000000002</v>
-      </c>
-      <c r="D37" s="21">
-        <v>0.61199999999999988</v>
-      </c>
-      <c r="E37" s="21">
-        <v>17.436</v>
-      </c>
-      <c r="F37" s="21">
-        <v>2.8980000000000001</v>
-      </c>
-      <c r="G37" s="21">
-        <v>224.24</v>
-      </c>
-      <c r="H37" s="21">
-        <v>222.81</v>
-      </c>
-      <c r="I37" s="21">
-        <v>99.36</v>
-      </c>
-      <c r="J37" s="21">
-        <v>1.4300000000000002</v>
-      </c>
-      <c r="K37" s="21">
-        <v>135.44881000000004</v>
-      </c>
-      <c r="L37" s="21">
-        <v>135.27241000000001</v>
-      </c>
-      <c r="M37" s="21">
-        <v>99.87</v>
-      </c>
-      <c r="N37" s="21">
-        <v>0.17641000000000004</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="46">
-        <v>1</v>
-      </c>
-      <c r="C38">
-        <v>3.15</v>
-      </c>
-      <c r="D38">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E38">
-        <v>17.59</v>
-      </c>
-      <c r="F38">
-        <v>2.6</v>
-      </c>
-      <c r="G38">
-        <v>200.42</v>
-      </c>
-      <c r="H38">
-        <v>199.17</v>
-      </c>
-      <c r="I38">
-        <v>99.38</v>
-      </c>
-      <c r="J38">
-        <v>1.25</v>
-      </c>
-      <c r="K38">
-        <v>135.4511</v>
-      </c>
-      <c r="L38">
-        <v>135.27420000000001</v>
-      </c>
-      <c r="M38">
-        <v>99.87</v>
-      </c>
-      <c r="N38">
-        <v>0.1769</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="46">
-        <v>2</v>
-      </c>
-      <c r="C39">
-        <v>5.35</v>
-      </c>
-      <c r="D39">
-        <v>0.84</v>
-      </c>
-      <c r="E39">
-        <v>15.78</v>
-      </c>
-      <c r="F39">
-        <v>4.51</v>
-      </c>
-      <c r="G39">
-        <v>287.37</v>
-      </c>
-      <c r="H39">
-        <v>286.06</v>
-      </c>
-      <c r="I39">
-        <v>99.54</v>
-      </c>
-      <c r="J39">
-        <v>1.31</v>
-      </c>
-      <c r="K39">
-        <v>169.92619999999999</v>
-      </c>
-      <c r="L39">
-        <v>169.7474</v>
-      </c>
-      <c r="M39">
-        <v>99.89</v>
-      </c>
-      <c r="N39">
-        <v>0.17879999999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="46">
-        <v>4</v>
-      </c>
-      <c r="C40">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="D40">
-        <v>1.58</v>
-      </c>
-      <c r="E40">
-        <v>15.48</v>
-      </c>
-      <c r="F40">
-        <v>8.6199999999999992</v>
-      </c>
-      <c r="G40">
-        <v>365.68</v>
-      </c>
-      <c r="H40">
-        <v>363.71</v>
-      </c>
-      <c r="I40">
-        <v>99.46</v>
-      </c>
-      <c r="J40">
-        <v>1.97</v>
-      </c>
-      <c r="K40">
-        <v>196.85040000000001</v>
-      </c>
-      <c r="L40">
-        <v>196.6678</v>
-      </c>
-      <c r="M40">
-        <v>99.91</v>
-      </c>
-      <c r="N40">
-        <v>0.18260000000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B41" s="46">
-        <v>8</v>
-      </c>
-      <c r="C41">
-        <v>20.75</v>
-      </c>
-      <c r="D41">
-        <v>3.42</v>
-      </c>
-      <c r="E41">
-        <v>16.489999999999998</v>
-      </c>
-      <c r="F41">
-        <v>17.329999999999998</v>
-      </c>
-      <c r="G41">
-        <v>521.07000000000005</v>
-      </c>
-      <c r="H41">
-        <v>519.44000000000005</v>
-      </c>
-      <c r="I41">
-        <v>99.69</v>
-      </c>
-      <c r="J41">
-        <v>1.63</v>
-      </c>
-      <c r="K41">
-        <v>250.2662</v>
-      </c>
-      <c r="L41">
-        <v>250.07669999999999</v>
-      </c>
-      <c r="M41">
-        <v>99.92</v>
-      </c>
-      <c r="N41">
-        <v>0.1895</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="47">
-        <v>16</v>
-      </c>
-      <c r="C42">
-        <v>49.41</v>
-      </c>
-      <c r="D42">
-        <v>8.0500000000000007</v>
-      </c>
-      <c r="E42">
-        <v>16.29</v>
-      </c>
-      <c r="F42">
-        <v>41.37</v>
-      </c>
-      <c r="G42">
-        <v>749.82</v>
-      </c>
-      <c r="H42">
-        <v>747.48</v>
-      </c>
-      <c r="I42">
-        <v>99.69</v>
-      </c>
-      <c r="J42">
-        <v>2.34</v>
-      </c>
-      <c r="K42">
-        <v>293.2978</v>
-      </c>
-      <c r="L42">
-        <v>293.09309999999999</v>
-      </c>
-      <c r="M42">
-        <v>99.93</v>
-      </c>
-      <c r="N42">
-        <v>0.20469999999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B43">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B44">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B45">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A47" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C48" s="58" t="s">
-        <v>85</v>
-      </c>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58" t="s">
-        <v>91</v>
-      </c>
-      <c r="H48" s="58"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="58"/>
-      <c r="K48" s="58" t="s">
-        <v>92</v>
-      </c>
-      <c r="L48" s="58"/>
-      <c r="M48" s="58"/>
-      <c r="N48" s="58"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>112</v>
-      </c>
-      <c r="B49" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="C49" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E49" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G49" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="H49" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="I49" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="J49" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="K49" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="L49" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="M49" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="N49" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>114</v>
-      </c>
-      <c r="B50" s="46" t="s">
-        <v>109</v>
-      </c>
-      <c r="C50" s="53">
-        <v>5.4716640000000005</v>
-      </c>
-      <c r="D50" s="27">
-        <v>2.573664</v>
-      </c>
-      <c r="E50" s="27">
-        <v>47.036221522374177</v>
-      </c>
-      <c r="F50" s="21">
-        <v>2.8980000000000001</v>
-      </c>
-      <c r="G50" s="21">
-        <f>J50+H50</f>
-        <v>109.35000000000001</v>
-      </c>
-      <c r="H50" s="27">
-        <v>107.92</v>
-      </c>
-      <c r="I50" s="27">
-        <v>98.692272519433004</v>
-      </c>
-      <c r="J50" s="21">
-        <v>1.4300000000000002</v>
-      </c>
-      <c r="K50" s="21">
-        <f>L50+N50</f>
-        <v>0.23746800000000004</v>
-      </c>
-      <c r="L50" s="27">
-        <v>6.1058000000000001E-2</v>
-      </c>
-      <c r="M50" s="27">
-        <v>25.712095945558978</v>
-      </c>
-      <c r="N50" s="21">
-        <v>0.17641000000000004</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B51" s="46">
-        <v>1</v>
-      </c>
-      <c r="C51" s="21">
-        <f>D51+F51</f>
-        <v>5.1736640000000005</v>
-      </c>
-      <c r="D51" s="27">
-        <v>2.573664</v>
-      </c>
-      <c r="E51" s="49"/>
-      <c r="F51">
-        <v>2.6</v>
-      </c>
-      <c r="G51" s="21">
-        <f t="shared" ref="G51:G55" si="3">J51+H51</f>
-        <v>109.17</v>
-      </c>
-      <c r="H51" s="27">
-        <v>107.92</v>
-      </c>
-      <c r="I51" s="49"/>
-      <c r="J51">
-        <v>1.25</v>
-      </c>
-      <c r="K51" s="21">
-        <f t="shared" ref="K51:K55" si="4">L51+N51</f>
-        <v>0.237958</v>
-      </c>
-      <c r="L51" s="27">
-        <v>6.1058000000000001E-2</v>
-      </c>
-      <c r="M51" s="50"/>
-      <c r="N51">
-        <v>0.1769</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>113</v>
-      </c>
-      <c r="B52" s="46">
-        <v>2</v>
-      </c>
-      <c r="C52" s="21">
-        <f t="shared" ref="C52:C55" si="5">D52+F52</f>
-        <v>8.9384049999999995</v>
-      </c>
-      <c r="D52">
-        <v>4.4284049999999997</v>
-      </c>
-      <c r="F52">
-        <v>4.51</v>
-      </c>
-      <c r="G52" s="21">
-        <f t="shared" si="3"/>
-        <v>118.17</v>
-      </c>
-      <c r="H52">
-        <v>116.86</v>
-      </c>
-      <c r="J52">
-        <v>1.31</v>
-      </c>
-      <c r="K52" s="21">
-        <f t="shared" si="4"/>
-        <v>0.24480199999999999</v>
-      </c>
-      <c r="L52" s="21">
-        <v>6.6002000000000005E-2</v>
-      </c>
-      <c r="M52" s="21"/>
-      <c r="N52">
-        <v>0.17879999999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>115</v>
-      </c>
-      <c r="B53" s="46">
-        <v>4</v>
-      </c>
-      <c r="C53" s="21">
-        <f t="shared" si="5"/>
-        <v>15.46932</v>
-      </c>
-      <c r="D53">
-        <v>6.8493200000000005</v>
-      </c>
-      <c r="F53">
-        <v>8.6199999999999992</v>
-      </c>
-      <c r="G53" s="21">
-        <f t="shared" si="3"/>
-        <v>117.89</v>
-      </c>
-      <c r="H53">
-        <v>115.92</v>
-      </c>
-      <c r="J53">
-        <v>1.97</v>
-      </c>
-      <c r="K53" s="21">
-        <f t="shared" si="4"/>
-        <v>0.24860200000000002</v>
-      </c>
-      <c r="L53" s="21">
-        <v>6.6002000000000005E-2</v>
-      </c>
-      <c r="M53" s="21"/>
-      <c r="N53">
-        <v>0.18260000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>116</v>
-      </c>
-      <c r="B54" s="46">
-        <v>8</v>
-      </c>
-      <c r="C54" s="21">
-        <f t="shared" si="5"/>
-        <v>29.06</v>
-      </c>
-      <c r="D54">
-        <v>11.73</v>
-      </c>
-      <c r="F54">
-        <v>17.329999999999998</v>
-      </c>
-      <c r="G54" s="21">
-        <f t="shared" si="3"/>
-        <v>125.85</v>
-      </c>
-      <c r="H54">
-        <v>124.22</v>
-      </c>
-      <c r="J54">
-        <v>1.63</v>
-      </c>
-      <c r="K54" s="21">
-        <f t="shared" si="4"/>
-        <v>0.26950000000000002</v>
-      </c>
-      <c r="L54" s="21">
-        <v>0.08</v>
-      </c>
-      <c r="N54">
-        <v>0.1895</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>117</v>
-      </c>
-      <c r="B55" s="47">
-        <v>16</v>
-      </c>
-      <c r="C55" s="21">
-        <f t="shared" si="5"/>
-        <v>60.9</v>
-      </c>
-      <c r="D55" s="3">
-        <v>19.53</v>
-      </c>
-      <c r="E55" s="3"/>
-      <c r="F55">
-        <v>41.37</v>
-      </c>
-      <c r="G55" s="21">
-        <f t="shared" si="3"/>
-        <v>126</v>
-      </c>
-      <c r="H55" s="3">
-        <v>123.66</v>
-      </c>
-      <c r="I55" s="3"/>
-      <c r="J55">
-        <v>2.34</v>
-      </c>
-      <c r="K55" s="21">
-        <f t="shared" si="4"/>
-        <v>0.28470000000000001</v>
-      </c>
-      <c r="L55" s="3">
-        <v>0.08</v>
-      </c>
-      <c r="M55" s="3"/>
-      <c r="N55">
-        <v>0.20469999999999999</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="K35:N35"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="G48:J48"/>
-    <mergeCell ref="K48:N48"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="K22:N22"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
 </file>
--- a/statistics/HasteBoots_Performance.xlsx
+++ b/statistics/HasteBoots_Performance.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/freya/Code/zkp/HasteBoots/statistics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD928BE-899D-DB4B-B01A-597CF417FC58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC60E463-7D47-8A46-A1A0-3C11EDC0BCCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34920" yWindow="-5740" windowWidth="33720" windowHeight="21100" activeTab="1" xr2:uid="{C673FD5D-B71E-674D-A3F8-C614E287E2BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 2" sheetId="2" r:id="rId1"/>
-    <sheet name="Table 4" sheetId="4" r:id="rId2"/>
+    <sheet name="Table 3" sheetId="4" r:id="rId2"/>
     <sheet name="PCS Perforamance" sheetId="3" r:id="rId3"/>
     <sheet name="FHE Parameters" sheetId="1" r:id="rId4"/>
   </sheets>
@@ -847,10 +847,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4391,24 +4391,24 @@
       <c r="X7" s="54"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C8" s="69" t="s">
+      <c r="C8" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69" t="s">
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="H8" s="69"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="69" t="s">
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="L8" s="69"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="69"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="68"/>
       <c r="O8" s="54"/>
       <c r="P8" s="54"/>
       <c r="Q8" s="54"/>
@@ -4884,24 +4884,24 @@
       <c r="X21" s="54"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="C22" s="69" t="s">
+      <c r="C22" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69" t="s">
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69" t="s">
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68" t="s">
         <v>92</v>
       </c>
-      <c r="L22" s="69"/>
-      <c r="M22" s="69"/>
-      <c r="N22" s="69"/>
+      <c r="L22" s="68"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="68"/>
       <c r="O22" s="54"/>
       <c r="P22" s="33" t="s">
         <v>68</v>
@@ -5411,18 +5411,18 @@
       <c r="C34" s="14"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C35" s="68"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="68"/>
-      <c r="H35" s="68"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="68"/>
-      <c r="K35" s="68"/>
-      <c r="L35" s="68"/>
-      <c r="M35" s="68"/>
-      <c r="N35" s="68"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="69"/>
+      <c r="L35" s="69"/>
+      <c r="M35" s="69"/>
+      <c r="N35" s="69"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C36" s="2"/>
@@ -5452,18 +5452,18 @@
       <c r="D47" s="14"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C48" s="68"/>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="68"/>
-      <c r="G48" s="68"/>
-      <c r="H48" s="68"/>
-      <c r="I48" s="68"/>
-      <c r="J48" s="68"/>
-      <c r="K48" s="68"/>
-      <c r="L48" s="68"/>
-      <c r="M48" s="68"/>
-      <c r="N48" s="68"/>
+      <c r="C48" s="69"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="69"/>
+      <c r="H48" s="69"/>
+      <c r="I48" s="69"/>
+      <c r="J48" s="69"/>
+      <c r="K48" s="69"/>
+      <c r="L48" s="69"/>
+      <c r="M48" s="69"/>
+      <c r="N48" s="69"/>
     </row>
     <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="2"/>
@@ -5524,18 +5524,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="K35:N35"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="G48:J48"/>
+    <mergeCell ref="K48:N48"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="K8:N8"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="G22:J22"/>
     <mergeCell ref="K22:N22"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="G35:J35"/>
-    <mergeCell ref="K35:N35"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="G48:J48"/>
-    <mergeCell ref="K48:N48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
